--- a/Solicitudes.xlsx
+++ b/Solicitudes.xlsx
@@ -5,29 +5,28 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\C25369\Documents\Huella\Automatizacion\Interconex\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\C65804\Desktop\Interconex\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8055" firstSheet="1" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8055" tabRatio="923" activeTab="5"/>
   </bookViews>
   <sheets>
-    <sheet name="Pago Móvil" sheetId="1" r:id="rId1"/>
-    <sheet name="Listar Bancos" sheetId="9" r:id="rId2"/>
-    <sheet name="Consulta Transferencias" sheetId="6" r:id="rId3"/>
-    <sheet name="Limites Transferencias" sheetId="7" r:id="rId4"/>
-    <sheet name="Transferencias" sheetId="2" r:id="rId5"/>
-    <sheet name="Consulta Límites Pago Móvil" sheetId="3" r:id="rId6"/>
-    <sheet name="Consulta Límite Transferencias" sheetId="4" r:id="rId7"/>
-    <sheet name="Lista De Movimientos" sheetId="5" r:id="rId8"/>
-    <sheet name="Limites Pago Movil" sheetId="8" r:id="rId9"/>
+    <sheet name="Transferencias" sheetId="2" r:id="rId1"/>
+    <sheet name="Pago Móvil" sheetId="1" r:id="rId2"/>
+    <sheet name="Listar Bancos" sheetId="9" r:id="rId3"/>
+    <sheet name="Consulta Transferencias" sheetId="6" r:id="rId4"/>
+    <sheet name="Limites Transferencias" sheetId="7" r:id="rId5"/>
+    <sheet name="Anulación C2P" sheetId="10" r:id="rId6"/>
+    <sheet name="Lista De Movimientos" sheetId="5" r:id="rId7"/>
+    <sheet name="Limites Pago Movil" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="97">
   <si>
     <t>Id Ordenante</t>
   </si>
@@ -137,12 +136,6 @@
     <t>idConsumidor</t>
   </si>
   <si>
-    <t>telefonoCliente</t>
-  </si>
-  <si>
-    <t>Id_Cliente</t>
-  </si>
-  <si>
     <t>Id_Canal</t>
   </si>
   <si>
@@ -182,9 +175,6 @@
     <t>J501540900</t>
   </si>
   <si>
-    <t>584120000001</t>
-  </si>
-  <si>
     <t>01150010241005756715</t>
   </si>
   <si>
@@ -285,6 +275,48 @@
   </si>
   <si>
     <t>P</t>
+  </si>
+  <si>
+    <t>idUsuario</t>
+  </si>
+  <si>
+    <t>idTerminal</t>
+  </si>
+  <si>
+    <t>idPagador</t>
+  </si>
+  <si>
+    <t>telfPagador</t>
+  </si>
+  <si>
+    <t>telfReceptor</t>
+  </si>
+  <si>
+    <t>ctaReceptor</t>
+  </si>
+  <si>
+    <t>serialOperacion</t>
+  </si>
+  <si>
+    <t>codBanco</t>
+  </si>
+  <si>
+    <t>terminal_beca</t>
+  </si>
+  <si>
+    <t>V1234567</t>
+  </si>
+  <si>
+    <t>584141234567</t>
+  </si>
+  <si>
+    <t>0115xxxxxxxxxxxxxxxx</t>
+  </si>
+  <si>
+    <t>10.5</t>
+  </si>
+  <si>
+    <t>pipe</t>
   </si>
 </sst>
 </file>
@@ -408,14 +440,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -425,8 +454,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -762,6 +789,136 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2">
+        <v>30</v>
+      </c>
+      <c r="H2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3">
+        <v>30</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1</v>
+      </c>
+      <c r="J3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -862,11 +1019,11 @@
       <c r="C3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="E3" s="24" t="s">
-        <v>76</v>
+      <c r="D3" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>73</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>21</v>
@@ -887,7 +1044,7 @@
         <v>31</v>
       </c>
       <c r="L3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -900,11 +1057,11 @@
       <c r="C4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>76</v>
+      <c r="D4" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>73</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>21</v>
@@ -925,7 +1082,7 @@
         <v>31</v>
       </c>
       <c r="L4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -938,11 +1095,11 @@
       <c r="C5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" s="24" t="s">
-        <v>76</v>
+      <c r="D5" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>73</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>21</v>
@@ -963,7 +1120,7 @@
         <v>31</v>
       </c>
       <c r="L5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -976,11 +1133,11 @@
       <c r="C6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>76</v>
+      <c r="D6" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>73</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>21</v>
@@ -1001,7 +1158,7 @@
         <v>31</v>
       </c>
       <c r="L6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1009,48 +1166,48 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="E1" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="F1" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="25" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="23">
+        <v>1</v>
+      </c>
+      <c r="C2" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="D2" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="F1" s="25" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" s="26">
-        <v>1</v>
-      </c>
-      <c r="C2" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="F2" s="26">
+      <c r="F2" s="23">
         <v>0</v>
       </c>
     </row>
@@ -1059,7 +1216,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1068,7 +1225,7 @@
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="15.140625" customWidth="1"/>
     <col min="4" max="4" width="18.85546875" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="22"/>
+    <col min="5" max="5" width="11.42578125" style="19"/>
     <col min="6" max="6" width="24.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17" bestFit="1" customWidth="1"/>
@@ -1079,129 +1236,129 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="E1" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="F1" s="17" t="s">
+      <c r="J1" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="L1" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="H1" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I1" s="17" t="s">
+      <c r="M1" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="J1" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="17" t="s">
+      <c r="N1" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="L1" s="17" t="s">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="15">
+        <v>1</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="17">
+        <v>46132</v>
+      </c>
+      <c r="F2" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="M1" s="17" t="s">
+      <c r="G2" s="15"/>
+      <c r="H2" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="N1" s="17" t="s">
+      <c r="I2" s="15">
+        <v>108</v>
+      </c>
+      <c r="J2" s="15" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+      <c r="K2" s="15"/>
+      <c r="L2" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="N2" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="15">
+        <v>1</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="17">
+        <v>46132</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15">
+        <v>115</v>
+      </c>
+      <c r="J3" s="15">
         <v>50</v>
       </c>
-      <c r="B2" s="18">
-        <v>1</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" s="20">
-        <v>46132</v>
-      </c>
-      <c r="F2" s="18" t="s">
+      <c r="K3" s="15"/>
+      <c r="L3" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="I2" s="18">
-        <v>108</v>
-      </c>
-      <c r="J2" s="18" t="s">
+      <c r="M3" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="M2" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="N2" s="18">
+      <c r="N3" s="15">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="18">
-        <v>1</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="20">
-        <v>46132</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18">
-        <v>115</v>
-      </c>
-      <c r="J3" s="18">
-        <v>50</v>
-      </c>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="M3" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="N3" s="18">
-        <v>0</v>
-      </c>
-    </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E10" s="21"/>
+      <c r="E10" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1209,7 +1366,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1219,30 +1376,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>72</v>
+      <c r="A1" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>49</v>
+      <c r="A2" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" s="10"/>
+        <v>67</v>
+      </c>
+      <c r="D2" s="7"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E4" s="10"/>
+      <c r="E4" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1250,225 +1407,216 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="7" max="8" width="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="C1" t="s">
-        <v>3</v>
+        <v>84</v>
       </c>
       <c r="D1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="F1" t="s">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="G1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>89</v>
+      </c>
+      <c r="L1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>96</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2">
+        <v>91005224827</v>
+      </c>
+      <c r="L2" t="s">
+        <v>95</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="G2">
-        <v>30</v>
-      </c>
-      <c r="H2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1</v>
-      </c>
-      <c r="J2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="20.42578125" customWidth="1"/>
-    <col min="4" max="4" width="24.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B2" s="7">
-        <v>1</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A128:D137"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" customWidth="1"/>
+    <col min="4" max="4" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" style="13" customWidth="1"/>
+    <col min="6" max="6" width="34.42578125" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="128" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B128" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C128" s="3" t="s">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D128" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A129" s="6" t="s">
+      <c r="F1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1" s="3"/>
+    </row>
+    <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="5">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B129">
+      <c r="E2" s="11">
+        <v>46189</v>
+      </c>
+      <c r="F2" s="5">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="5">
         <v>1</v>
       </c>
-      <c r="D129" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A130" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B130">
+      <c r="C3" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="12">
+        <v>46189</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="5">
         <v>1</v>
       </c>
-      <c r="D130" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A131" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B131">
-        <v>1</v>
-      </c>
-      <c r="D131" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A132" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B132">
-        <v>1</v>
-      </c>
-      <c r="D132" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A133" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B133">
-        <v>1</v>
-      </c>
-      <c r="D133" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B137" s="10"/>
+      <c r="C4" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="12">
+        <v>46189</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="7"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F14" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1477,122 +1625,6 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" customWidth="1"/>
-    <col min="4" max="4" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.28515625" style="16" customWidth="1"/>
-    <col min="6" max="6" width="34.42578125" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="J1" s="4"/>
-    </row>
-    <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B2" s="6">
-        <v>1</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="14">
-        <v>46189</v>
-      </c>
-      <c r="F2" s="6">
-        <v>0</v>
-      </c>
-      <c r="G2" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B3" s="6">
-        <v>1</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="15">
-        <v>46189</v>
-      </c>
-      <c r="F3" s="6">
-        <v>0</v>
-      </c>
-      <c r="G3" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B4" s="6">
-        <v>1</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="15">
-        <v>46189</v>
-      </c>
-      <c r="F4" s="6">
-        <v>0</v>
-      </c>
-      <c r="G4" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B7" s="10"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F14" s="12"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1603,21 +1635,21 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1626,11 +1658,11 @@
         <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C7" s="10"/>
+      <c r="C7" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Solicitudes.xlsx
+++ b/Solicitudes.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\C25369\Documents\Huella\Automatizacion\Interconex\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\C65805\Documents\GitHub\Interconex\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8055" firstSheet="1" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8055" firstSheet="5" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Pago Móvil" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,15 @@
     <sheet name="Consulta Límites Pago Móvil" sheetId="3" r:id="rId6"/>
     <sheet name="Consulta Límite Transferencias" sheetId="4" r:id="rId7"/>
     <sheet name="Lista De Movimientos" sheetId="5" r:id="rId8"/>
-    <sheet name="Limites Pago Movil" sheetId="8" r:id="rId9"/>
+    <sheet name="Cobro_comercio_C2P" sheetId="10" r:id="rId9"/>
+    <sheet name="Limites Pago Movil" sheetId="8" r:id="rId10"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="112">
   <si>
     <t>Id Ordenante</t>
   </si>
@@ -185,15 +186,6 @@
     <t>584120000001</t>
   </si>
   <si>
-    <t>01150010241005756715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J085371427 </t>
-  </si>
-  <si>
-    <t>01150063311002276299</t>
-  </si>
-  <si>
     <t>E123456</t>
   </si>
   <si>
@@ -285,6 +277,135 @@
   </si>
   <si>
     <t>P</t>
+  </si>
+  <si>
+    <t>01150010271005758504</t>
+  </si>
+  <si>
+    <t>J303770649</t>
+  </si>
+  <si>
+    <t>J500650043</t>
+  </si>
+  <si>
+    <t>El RIF del Comercio (Receptor del dinero).</t>
+  </si>
+  <si>
+    <t>Canal de la transacción. El script lo adapta para cada API automáticamente.</t>
+  </si>
+  <si>
+    <t>Identificador técnico del consumidor.</t>
+  </si>
+  <si>
+    <t>id_pagador</t>
+  </si>
+  <si>
+    <t>V7180776</t>
+  </si>
+  <si>
+    <r>
+      <t>La cédula o RIF de la persona que va a pagar (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fase 1 y Fase 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <t>telf_pagador</t>
+  </si>
+  <si>
+    <r>
+      <t>Teléfono afiliado de quien paga (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Usado para buscar la OTP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <t>telf_receptor</t>
+  </si>
+  <si>
+    <t>Teléfono del comercio que recibe el pago.</t>
+  </si>
+  <si>
+    <t>cta_receptor</t>
+  </si>
+  <si>
+    <t>Cuenta bancaria de 20 dígitos del comercio.</t>
+  </si>
+  <si>
+    <t>Tipo de moneda (usualmente bolívares).</t>
+  </si>
+  <si>
+    <t>concepto</t>
+  </si>
+  <si>
+    <t>pago material</t>
+  </si>
+  <si>
+    <t>Motivo o descripción de la transacción.</t>
+  </si>
+  <si>
+    <t>10.5</t>
+  </si>
+  <si>
+    <t>El monto numérico a cobrar (puedes usar decimales con punto).</t>
+  </si>
+  <si>
+    <t>cod_banco</t>
+  </si>
+  <si>
+    <t>Los primeros 4 dígitos del banco receptor.</t>
+  </si>
+  <si>
+    <t>04143391197</t>
+  </si>
+  <si>
+    <t>01150010221005750000</t>
+  </si>
+  <si>
+    <t>04122877725</t>
+  </si>
+  <si>
+    <t>P35525379</t>
+  </si>
+  <si>
+    <t>01150010261005759029</t>
+  </si>
+  <si>
+    <t>04168963627</t>
   </si>
 </sst>
 </file>
@@ -295,7 +416,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -334,12 +455,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF8B949E"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -357,6 +472,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Google Sans Text"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Bookman Old Style"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -366,7 +506,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -404,11 +544,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -428,23 +592,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -456,10 +615,32 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -763,7 +944,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
@@ -776,7 +957,7 @@
     <col min="11" max="11" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -814,7 +995,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -852,7 +1033,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -862,11 +1043,11 @@
       <c r="C3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="E3" s="24" t="s">
-        <v>76</v>
+      <c r="D3" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>73</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>21</v>
@@ -887,10 +1068,10 @@
         <v>31</v>
       </c>
       <c r="L3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -900,11 +1081,11 @@
       <c r="C4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>76</v>
+      <c r="D4" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>73</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>21</v>
@@ -925,10 +1106,10 @@
         <v>31</v>
       </c>
       <c r="L4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -938,11 +1119,11 @@
       <c r="C5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" s="24" t="s">
-        <v>76</v>
+      <c r="D5" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>73</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>21</v>
@@ -963,10 +1144,10 @@
         <v>31</v>
       </c>
       <c r="L5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -976,11 +1157,11 @@
       <c r="C6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>76</v>
+      <c r="D6" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>73</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>21</v>
@@ -1001,56 +1182,102 @@
         <v>31</v>
       </c>
       <c r="L6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="C7" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="E1" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="F1" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="25" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="23">
+        <v>1</v>
+      </c>
+      <c r="C2" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="D2" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="F1" s="25" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" s="26">
-        <v>1</v>
-      </c>
-      <c r="C2" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="F2" s="26">
+      <c r="F2" s="23">
         <v>0</v>
       </c>
     </row>
@@ -1062,13 +1289,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.140625" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="15.140625" customWidth="1"/>
     <col min="4" max="4" width="18.85546875" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="22"/>
+    <col min="5" max="5" width="11.42578125" style="19"/>
     <col min="6" max="6" width="24.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17" bestFit="1" customWidth="1"/>
@@ -1078,130 +1305,130 @@
     <col min="14" max="14" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="E1" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="F1" s="17" t="s">
+      <c r="J1" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="L1" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="H1" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I1" s="17" t="s">
+      <c r="M1" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="J1" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="17" t="s">
+      <c r="N1" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="L1" s="17" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="15">
+        <v>1</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="17">
+        <v>46132</v>
+      </c>
+      <c r="F2" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="M1" s="17" t="s">
+      <c r="G2" s="15"/>
+      <c r="H2" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="N1" s="17" t="s">
+      <c r="I2" s="15">
+        <v>108</v>
+      </c>
+      <c r="J2" s="15" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+      <c r="K2" s="15"/>
+      <c r="L2" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="N2" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="18">
-        <v>1</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" s="18" t="s">
+      <c r="B3" s="15">
+        <v>1</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="17">
+        <v>46132</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15">
+        <v>115</v>
+      </c>
+      <c r="J3" s="15">
         <v>50</v>
       </c>
-      <c r="E2" s="20">
-        <v>46132</v>
-      </c>
-      <c r="F2" s="18" t="s">
+      <c r="K3" s="15"/>
+      <c r="L3" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="I2" s="18">
-        <v>108</v>
-      </c>
-      <c r="J2" s="18" t="s">
+      <c r="M3" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="M2" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="N2" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="18">
-        <v>1</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="20">
-        <v>46132</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18">
-        <v>115</v>
-      </c>
-      <c r="J3" s="18">
-        <v>50</v>
-      </c>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="M3" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="N3" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E10" s="21"/>
+      <c r="N3" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="E10" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1212,24 +1439,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.75">
       <c r="A2" s="6" t="s">
         <v>49</v>
       </c>
@@ -1237,11 +1464,11 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D2" s="10"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="E4" s="10"/>
     </row>
   </sheetData>
@@ -1253,7 +1480,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
@@ -1267,7 +1494,7 @@
     <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -1305,7 +1532,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -1348,13 +1575,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="20.42578125" customWidth="1"/>
     <col min="4" max="4" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" s="3" t="s">
         <v>33</v>
       </c>
@@ -1368,7 +1595,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15.75">
       <c r="A2" s="8" t="s">
         <v>50</v>
       </c>
@@ -1390,7 +1617,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A128:D137"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
@@ -1398,7 +1625,7 @@
     <col min="4" max="4" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="128" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" ht="14.25" customHeight="1">
       <c r="A128" s="3" t="s">
         <v>37</v>
       </c>
@@ -1412,7 +1639,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" ht="15.75">
       <c r="A129" s="6" t="s">
         <v>49</v>
       </c>
@@ -1423,7 +1650,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" ht="15.75">
       <c r="A130" s="6" t="s">
         <v>49</v>
       </c>
@@ -1434,7 +1661,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" ht="15.75">
       <c r="A131" s="6" t="s">
         <v>49</v>
       </c>
@@ -1445,7 +1672,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" ht="15.75">
       <c r="A132" s="6" t="s">
         <v>49</v>
       </c>
@@ -1456,7 +1683,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" ht="15.75">
       <c r="A133" s="6" t="s">
         <v>49</v>
       </c>
@@ -1467,7 +1694,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4">
       <c r="B137" s="10"/>
     </row>
   </sheetData>
@@ -1478,18 +1705,18 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
     <col min="4" max="4" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.28515625" style="16" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" style="13" customWidth="1"/>
     <col min="6" max="6" width="34.42578125" customWidth="1"/>
     <col min="9" max="9" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
       <c r="A1" s="5" t="s">
         <v>42</v>
       </c>
@@ -1502,7 +1729,7 @@
       <c r="D1" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="11" t="s">
         <v>41</v>
       </c>
       <c r="F1" s="5" t="s">
@@ -1513,9 +1740,9 @@
       </c>
       <c r="J1" s="4"/>
     </row>
-    <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>50</v>
+    <row r="2" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A2" t="s">
+        <v>84</v>
       </c>
       <c r="B2" s="6">
         <v>1</v>
@@ -1523,11 +1750,11 @@
       <c r="C2" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="14">
-        <v>46189</v>
+      <c r="D2" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" s="12">
+        <v>46143</v>
       </c>
       <c r="F2" s="6">
         <v>0</v>
@@ -1536,21 +1763,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>49</v>
+    <row r="3" spans="1:10" ht="15.75">
+      <c r="A3" t="s">
+        <v>84</v>
       </c>
       <c r="B3" s="6">
         <v>1</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="15">
-        <v>46189</v>
+        <v>48</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" s="12">
+        <v>46144</v>
       </c>
       <c r="F3" s="6">
         <v>0</v>
@@ -1559,19 +1786,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>53</v>
+    <row r="4" spans="1:10" ht="15.75">
+      <c r="A4" t="s">
+        <v>84</v>
       </c>
       <c r="B4" s="6">
         <v>1</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="15">
-        <v>46189</v>
+        <v>48</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" s="12">
+        <v>46145</v>
       </c>
       <c r="F4" s="6">
         <v>0</v>
@@ -1580,11 +1809,649 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B7" s="10"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F14" s="12"/>
+    <row r="5" spans="1:10" ht="15.75">
+      <c r="A5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" s="6">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" s="12">
+        <v>46146</v>
+      </c>
+      <c r="F5" s="6">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.75">
+      <c r="A6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="12">
+        <v>46147</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.75">
+      <c r="A7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="6">
+        <v>1</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E7" s="12">
+        <v>46148</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75">
+      <c r="A8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="6">
+        <v>1</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="12">
+        <v>46149</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.75">
+      <c r="A9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="6">
+        <v>1</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="12">
+        <v>46150</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15.75">
+      <c r="A10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="6">
+        <v>1</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="12">
+        <v>46151</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15.75">
+      <c r="A11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="6">
+        <v>1</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="12">
+        <v>46152</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15.75">
+      <c r="A12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="6">
+        <v>1</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F12" s="6">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15.75">
+      <c r="A13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" s="6">
+        <v>1</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F13" s="6">
+        <v>0</v>
+      </c>
+      <c r="G13" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15.75">
+      <c r="A14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="6">
+        <v>1</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="12">
+        <v>46155</v>
+      </c>
+      <c r="F14" s="6">
+        <v>0</v>
+      </c>
+      <c r="G14" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15.75">
+      <c r="A15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="6">
+        <v>1</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" s="12">
+        <v>46156</v>
+      </c>
+      <c r="F15" s="6">
+        <v>0</v>
+      </c>
+      <c r="G15" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15.75">
+      <c r="A16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="6">
+        <v>1</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" s="12">
+        <v>46157</v>
+      </c>
+      <c r="F16" s="6">
+        <v>0</v>
+      </c>
+      <c r="G16" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.75">
+      <c r="A17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" s="6">
+        <v>1</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="12">
+        <v>46158</v>
+      </c>
+      <c r="F17" s="6">
+        <v>0</v>
+      </c>
+      <c r="G17" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.75">
+      <c r="A18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" s="6">
+        <v>1</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E18" s="12">
+        <v>46159</v>
+      </c>
+      <c r="F18" s="6">
+        <v>0</v>
+      </c>
+      <c r="G18" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75">
+      <c r="A19" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19" s="6">
+        <v>1</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" s="12">
+        <v>46160</v>
+      </c>
+      <c r="F19" s="6">
+        <v>0</v>
+      </c>
+      <c r="G19" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.75">
+      <c r="A20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" s="6">
+        <v>1</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="12">
+        <v>46161</v>
+      </c>
+      <c r="F20" s="6">
+        <v>0</v>
+      </c>
+      <c r="G20" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.75">
+      <c r="A21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" s="6">
+        <v>1</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" s="12">
+        <v>46162</v>
+      </c>
+      <c r="F21" s="6">
+        <v>0</v>
+      </c>
+      <c r="G21" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75">
+      <c r="A22" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" s="6">
+        <v>1</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22" s="12">
+        <v>46163</v>
+      </c>
+      <c r="F22" s="6">
+        <v>0</v>
+      </c>
+      <c r="G22" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.75">
+      <c r="A23" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" s="6">
+        <v>1</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" s="12">
+        <v>46164</v>
+      </c>
+      <c r="F23" s="6">
+        <v>0</v>
+      </c>
+      <c r="G23" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75">
+      <c r="A24" t="s">
+        <v>84</v>
+      </c>
+      <c r="B24" s="6">
+        <v>1</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" s="12">
+        <v>46165</v>
+      </c>
+      <c r="F24" s="6">
+        <v>0</v>
+      </c>
+      <c r="G24" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75">
+      <c r="A25" t="s">
+        <v>84</v>
+      </c>
+      <c r="B25" s="6">
+        <v>1</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E25" s="12">
+        <v>46166</v>
+      </c>
+      <c r="F25" s="6">
+        <v>0</v>
+      </c>
+      <c r="G25" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75">
+      <c r="A26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" s="6">
+        <v>1</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E26" s="12">
+        <v>46167</v>
+      </c>
+      <c r="F26" s="6">
+        <v>0</v>
+      </c>
+      <c r="G26" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75">
+      <c r="A27" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" s="6">
+        <v>1</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" s="12">
+        <v>46168</v>
+      </c>
+      <c r="F27" s="6">
+        <v>0</v>
+      </c>
+      <c r="G27" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.75">
+      <c r="A28" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" s="6">
+        <v>1</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D28" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E28" s="12">
+        <v>46169</v>
+      </c>
+      <c r="F28" s="6">
+        <v>0</v>
+      </c>
+      <c r="G28" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.75">
+      <c r="A29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" s="6">
+        <v>1</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D29" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E29" s="12">
+        <v>46170</v>
+      </c>
+      <c r="F29" s="6">
+        <v>0</v>
+      </c>
+      <c r="G29" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.75">
+      <c r="A30" t="s">
+        <v>84</v>
+      </c>
+      <c r="B30" s="6">
+        <v>1</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D30" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E30" s="12">
+        <v>46171</v>
+      </c>
+      <c r="F30" s="6">
+        <v>0</v>
+      </c>
+      <c r="G30" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.75">
+      <c r="A31" t="s">
+        <v>84</v>
+      </c>
+      <c r="B31" s="6">
+        <v>1</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D31" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E31" s="12">
+        <v>46172</v>
+      </c>
+      <c r="F31" s="6">
+        <v>0</v>
+      </c>
+      <c r="G31" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75">
+      <c r="A32" t="s">
+        <v>84</v>
+      </c>
+      <c r="B32" s="6">
+        <v>1</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D32" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E32" s="12">
+        <v>46173</v>
+      </c>
+      <c r="F32" s="6">
+        <v>0</v>
+      </c>
+      <c r="G32" s="6">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1594,43 +2461,181 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" customWidth="1"/>
+    <col min="5" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="13" max="13" width="73.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="1" spans="1:13" ht="29.25" thickBot="1">
+      <c r="A1" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="J1" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="M1" s="28" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="29.25" thickBot="1">
+      <c r="A2" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="30">
+        <v>1</v>
+      </c>
+      <c r="C2" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="D2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C7" s="10"/>
+      <c r="D2" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="G2" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="H2" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="J2" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="K2" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="27" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="29.25" thickBot="1">
+      <c r="A3" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="15">
+        <v>1</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H3" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="J3" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="K3" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" s="27" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="M4" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="K5" s="10"/>
+      <c r="M5" s="27" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="K6" s="10"/>
+      <c r="M6" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="M7" s="27" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="M8" s="27" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="M9" s="27" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="M10" s="27" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="M11" s="27" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="M12" s="27" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="L13" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Solicitudes.xlsx
+++ b/Solicitudes.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8055" firstSheet="5" activeTab="9"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8055" firstSheet="5" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Limites Pago Movil" sheetId="8" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="120">
   <si>
     <t>Id Ordenante</t>
   </si>
@@ -267,9 +267,6 @@
     <t>J303770649</t>
   </si>
   <si>
-    <t>J500650043</t>
-  </si>
-  <si>
     <t>El RIF del Comercio (Receptor del dinero).</t>
   </si>
   <si>
@@ -280,9 +277,6 @@
   </si>
   <si>
     <t>id_pagador</t>
-  </si>
-  <si>
-    <t>V7180776</t>
   </si>
   <si>
     <r>
@@ -360,9 +354,6 @@
     <t>Motivo o descripción de la transacción.</t>
   </si>
   <si>
-    <t>10.5</t>
-  </si>
-  <si>
     <t>El monto numérico a cobrar (puedes usar decimales con punto).</t>
   </si>
   <si>
@@ -372,15 +363,6 @@
     <t>Los primeros 4 dígitos del banco receptor.</t>
   </si>
   <si>
-    <t>01150010221005750000</t>
-  </si>
-  <si>
-    <t>P35525379</t>
-  </si>
-  <si>
-    <t>01150010261005759029</t>
-  </si>
-  <si>
     <t>id_cliente_otp</t>
   </si>
   <si>
@@ -396,12 +378,6 @@
     <t>V25796849</t>
   </si>
   <si>
-    <t>cuenta_origen</t>
-  </si>
-  <si>
-    <t>nombre_debito</t>
-  </si>
-  <si>
     <t>nombre_pagador</t>
   </si>
   <si>
@@ -417,31 +393,43 @@
     <t>Juan de Dios</t>
   </si>
   <si>
-    <t>cuenta_debito</t>
-  </si>
-  <si>
     <t>Pedro</t>
   </si>
   <si>
-    <t>584249265154</t>
-  </si>
-  <si>
     <t>serial_operacion</t>
   </si>
   <si>
-    <t>J132456789</t>
-  </si>
-  <si>
-    <t>V123456789</t>
-  </si>
-  <si>
-    <t>0414321655</t>
-  </si>
-  <si>
-    <t>04123391197</t>
-  </si>
-  <si>
-    <t>01155646546546546556</t>
+    <t>cuenta_credito</t>
+  </si>
+  <si>
+    <t>nombre_credito</t>
+  </si>
+  <si>
+    <t>cuenta_pagador</t>
+  </si>
+  <si>
+    <t>584241062053</t>
+  </si>
+  <si>
+    <t>E82118380</t>
+  </si>
+  <si>
+    <t>01150021891005730165</t>
+  </si>
+  <si>
+    <t>J300180174</t>
+  </si>
+  <si>
+    <t>584149105125</t>
+  </si>
+  <si>
+    <t>04241062053</t>
+  </si>
+  <si>
+    <t>04149105125</t>
+  </si>
+  <si>
+    <t>telefono_pagador</t>
   </si>
 </sst>
 </file>
@@ -608,7 +596,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -665,12 +653,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
@@ -1026,74 +1008,85 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="29" t="s">
-        <v>83</v>
-      </c>
-      <c r="E1" s="29" t="s">
+      <c r="D1" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="F1" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="G1" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="G1" s="29" t="s">
-        <v>90</v>
-      </c>
-      <c r="H1" s="29" t="s">
+      <c r="H1" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="29" t="s">
+      <c r="I1" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="J1" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="27" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="28">
+        <v>1</v>
+      </c>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="E2" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="J1" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="29" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B2" s="6">
-        <v>1</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="E2" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="F2" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="G2" s="30" t="s">
-        <v>123</v>
+      <c r="G2" s="28" t="s">
+        <v>114</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="6">
-        <v>3213546</v>
+        <v>91005317978</v>
       </c>
       <c r="J2" s="6">
-        <v>100</v>
-      </c>
-      <c r="K2" s="30" t="s">
+        <v>10.5</v>
+      </c>
+      <c r="K2" s="28" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2445,7 +2438,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.140625" customWidth="1"/>
@@ -2460,19 +2453,19 @@
     <col min="10" max="10" width="17.7109375" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
     <col min="12" max="12" width="18.28515625" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" customWidth="1"/>
+    <col min="13" max="13" width="17" customWidth="1"/>
     <col min="14" max="14" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D1" t="s">
         <v>70</v>
@@ -2481,58 +2474,67 @@
         <v>7</v>
       </c>
       <c r="F1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="H1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="K1" t="s">
         <v>72</v>
       </c>
       <c r="L1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+        <v>111</v>
+      </c>
+      <c r="M1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>78</v>
       </c>
       <c r="B2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1.5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J2" t="s">
         <v>107</v>
       </c>
-      <c r="C2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>113</v>
-      </c>
-      <c r="G2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H2" t="s">
-        <v>114</v>
-      </c>
-      <c r="I2" t="s">
-        <v>111</v>
-      </c>
-      <c r="J2" t="s">
-        <v>116</v>
-      </c>
+      <c r="M2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="G5" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2565,154 +2567,121 @@
         <v>72</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E1" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="F1" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="G1" s="22" t="s">
         <v>88</v>
-      </c>
-      <c r="G1" s="22" t="s">
-        <v>90</v>
       </c>
       <c r="H1" s="22" t="s">
         <v>8</v>
       </c>
       <c r="I1" s="22" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J1" s="22" t="s">
         <v>7</v>
       </c>
       <c r="K1" s="22" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="M1" s="25" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="29.25" thickBot="1">
-      <c r="A2" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="B2" s="27">
-        <v>1</v>
-      </c>
-      <c r="C2" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>117</v>
+      <c r="A2" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="26">
+        <v>1</v>
+      </c>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>116</v>
       </c>
       <c r="G2" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="H2" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="H2" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="J2" s="22" t="s">
-        <v>96</v>
+      <c r="I2" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="J2" s="26">
+        <v>20</v>
       </c>
       <c r="K2" s="26" t="s">
         <v>21</v>
       </c>
       <c r="M2" s="24" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="M3" s="24" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="29.25" thickBot="1">
-      <c r="A3" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="B3" s="12">
-        <v>1</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="H3" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="J3" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="K3" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3" s="24" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="M4" s="24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="K5" s="7"/>
       <c r="M5" s="24" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="K6" s="7"/>
       <c r="M6" s="24" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="M7" s="24" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="M8" s="24" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="M9" s="24" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="M10" s="24" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="M11" s="24" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="M12" s="24" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:13">
